--- a/output_tcc_var/tabelas/testes_estacionariedade_nivel_e_diff.xlsx
+++ b/output_tcc_var/tabelas/testes_estacionariedade_nivel_e_diff.xlsx
@@ -478,16 +478,16 @@
         <v>273</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.140218382747632</v>
+        <v>-1.140227044038539</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9220520655295787</v>
+        <v>0.9220504911557919</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5566098394239688</v>
+        <v>0.5566047327046335</v>
       </c>
       <c r="H2" t="n">
         <v>0.01</v>
@@ -511,16 +511,16 @@
         <v>272</v>
       </c>
       <c r="D3" t="n">
-        <v>-3.12602255203366</v>
+        <v>-3.125995290699515</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02468638630990705</v>
+        <v>0.02468828124471295</v>
       </c>
       <c r="F3" t="n">
         <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>1.08124661547293</v>
+        <v>1.081188784060267</v>
       </c>
       <c r="H3" t="n">
         <v>0.01</v>
@@ -742,16 +742,16 @@
         <v>273</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.804837175254419</v>
+        <v>-1.804837175254416</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7024212209547631</v>
+        <v>0.7024212209547647</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5333574058467738</v>
+        <v>0.5333574058467783</v>
       </c>
       <c r="H10" t="n">
         <v>0.01</v>
@@ -775,16 +775,16 @@
         <v>272</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.258378445753237</v>
+        <v>-9.258378445753236</v>
       </c>
       <c r="E11" t="n">
-        <v>1.429063097055548e-15</v>
+        <v>1.429063097055579e-15</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2618932474346328</v>
+        <v>0.2618932474346323</v>
       </c>
       <c r="H11" t="n">
         <v>0.1</v>
@@ -808,19 +808,19 @@
         <v>273</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.521626683348284</v>
+        <v>-2.975238134299429</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3172354233401663</v>
+        <v>0.1391359430321656</v>
       </c>
       <c r="F12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2338201154236288</v>
+        <v>0.1341423069716602</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01</v>
+        <v>0.07195869079322187</v>
       </c>
       <c r="I12" t="n">
         <v>10</v>
@@ -841,22 +841,22 @@
         <v>272</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.317946804703787</v>
+        <v>-3.68012708130705</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01409506490876927</v>
+        <v>0.004401528530182189</v>
       </c>
       <c r="F13" t="n">
         <v>13</v>
       </c>
       <c r="G13" t="n">
-        <v>0.09370778146934378</v>
+        <v>0.1088616400054755</v>
       </c>
       <c r="H13" t="n">
         <v>0.1</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -874,16 +874,16 @@
         <v>273</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.452611626406048</v>
+        <v>-3.452611626406054</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04474531456257509</v>
+        <v>0.04474531456257449</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4395809144506881</v>
+        <v>0.4395809144506911</v>
       </c>
       <c r="H14" t="n">
         <v>0.01</v>
@@ -907,7 +907,7 @@
         <v>272</v>
       </c>
       <c r="D15" t="n">
-        <v>-9.168128544982038</v>
+        <v>-9.168128544982036</v>
       </c>
       <c r="E15" t="n">
         <v>2.429240648478783e-15</v>
@@ -916,7 +916,7 @@
         <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07942505097812975</v>
+        <v>0.0794250509781296</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
@@ -940,16 +940,16 @@
         <v>273</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.813215993013438</v>
+        <v>-3.813215993013441</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0159035035041383</v>
+        <v>0.0159035035041381</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2813906260219138</v>
+        <v>0.2813906260219103</v>
       </c>
       <c r="H16" t="n">
         <v>0.01</v>
@@ -976,13 +976,13 @@
         <v>-11.57815718438281</v>
       </c>
       <c r="E17" t="n">
-        <v>2.987557968249015e-21</v>
+        <v>2.987557968248906e-21</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05135042362996755</v>
+        <v>0.05135042362996711</v>
       </c>
       <c r="H17" t="n">
         <v>0.1</v>
@@ -1006,16 +1006,16 @@
         <v>273</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.680664102079886</v>
+        <v>-1.680664102079883</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7592756749083476</v>
+        <v>0.7592756749083488</v>
       </c>
       <c r="F18" t="n">
         <v>11</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4588500916614396</v>
+        <v>0.4588500916614398</v>
       </c>
       <c r="H18" t="n">
         <v>0.01</v>
@@ -1039,16 +1039,16 @@
         <v>272</v>
       </c>
       <c r="D19" t="n">
-        <v>-5.910726265206343</v>
+        <v>-5.910726265206345</v>
       </c>
       <c r="E19" t="n">
-        <v>2.642768898932398e-07</v>
+        <v>2.642768898932373e-07</v>
       </c>
       <c r="F19" t="n">
         <v>10</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1525667858304672</v>
+        <v>0.1525667858304668</v>
       </c>
       <c r="H19" t="n">
         <v>0.1</v>
